--- a/daily_matches/job_matches_2026-10-03.xlsx
+++ b/daily_matches/job_matches_2026-10-03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Digital Software Engineer Intermediate Analyst</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, scikit-learn, XGBoost, BigQuery, Dataflow</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,32 +484,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c7ac7363c390d2</t>
+          <t>https://www.indeed.com/viewjob?jk=4f502a72aa366cf5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>TGS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, scikit-learn, XGBoost, BigQuery, Dataflow</t>
+          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,32 +519,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=466d7045497ccea0</t>
+          <t>https://www.indeed.com/viewjob?jk=6251b84b65aed773</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Engineer, IT AI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Carlos, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, S3, Glue, Athena, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>Generative AI, RAG, LLaMA, Gemini, Copilot, Docker, Jenkins, Git, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,32 +554,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42cd837866eddbf4</t>
+          <t>https://www.indeed.com/viewjob?jk=6da4b0626ba24d7d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer Associate Consultant</t>
+          <t>Senior Full Stack Developer - Java, Angular</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, S3, Redshift, Docker, Kubernetes, AKS, Terraform</t>
+          <t>LangChain, RAG, S3, CI/CD, Git, Kafka, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,32 +589,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb36d41ad52a06bd</t>
+          <t>https://www.indeed.com/viewjob?jk=f75183eedc15fcaa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Hadoop Solutions Developer</t>
+          <t>Advanced Software Engineer - AI Platform</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Relativity</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
+          <t>MLflow, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,32 +624,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68c24b0124716a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=68b63ee7b7ca6842</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Rice University</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Miami Beach, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Docker, CI/CD, GitHub Actions, Terraform, Git, BigQuery, PostgreSQL, MySQL</t>
+          <t>Data Scientist, RAG, FAISS, PyTorch, S3, Data Lake, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,32 +659,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef02d35010b82b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=c35c7cc0f98c8cb5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Platform Engineer II/III</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MAPFRE Insurance</t>
+          <t>Rice Engineering</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Webster, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Data Scientist, RAG, FAISS, PyTorch, S3, Data Lake, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eeeb83b5522fc44</t>
+          <t>https://www.indeed.com/viewjob?jk=3d79a4934cb33cf2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>Simulation Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Xenith Solutions</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, FastAPI, Docker, Kubernetes, Git, Kafka, PostgreSQL, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,32 +729,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db196ca6501ae65b</t>
+          <t>https://www.indeed.com/viewjob?jk=b856865fd8381428</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI &amp; Agentic Architecture</t>
+          <t>Data Science Co-Op (NLP &amp; GenAI)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sony Interactive Entertainment</t>
+          <t>Bose</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Framingham, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
+          <t>LangChain, RAG, LLaMA, Hugging Face, scikit-learn, MLflow, Git, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,32 +764,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141250f8080f4044</t>
+          <t>https://www.indeed.com/viewjob?jk=a19382d40f0c41f5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Application/DevOps Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GA Telesis</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, BigQuery, CI/CD, Git, BigQuery, Python, SQL, R</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,102 +799,102 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfd341b35c80136f</t>
+          <t>https://www.indeed.com/viewjob?jk=9d78fc9cce74c619</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Snowflake, Kafka, SQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, Azure ML, Snowflake, Databricks, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=607e2aeb25bf6f87</t>
+          <t>https://www.indeed.com/viewjob?jk=65d759c6cb21fb15</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Georgia-Pacific</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New Bedford, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>S3, FastAPI, Docker, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, S3, Data Lake, CI/CD, Terraform, Git, Databricks, Python, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2689f756f071cb85</t>
+          <t>https://www.indeed.com/viewjob?jk=3a085e8b62912626</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sentinel Group</t>
+          <t>HealthStream</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Python, SQL</t>
+          <t>RAG, Copilot, Prompt Engineering, S3, EC2, CI/CD, Git, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,32 +904,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e995e33ef6181c97</t>
+          <t>https://www.indeed.com/viewjob?jk=01050adb3573b7dc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marketing Data Analyst</t>
+          <t>Software Engineer, Backend â€“ Webex Signaling</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hoover Institution, Stanford University</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Stanford, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BigQuery, CI/CD, GitHub Actions, Git, BigQuery, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Kubernetes, CI/CD, Git, Kafka, Cassandra, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,24 +939,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e021664b78377650</t>
+          <t>https://www.indeed.com/viewjob?jk=4e1b2b0f782a362c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>World View</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -964,7 +964,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, PostgreSQL, MongoDB, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, S3, Kinesis, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,32 +974,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17fce9c056aead2f</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c0b1ce938721b8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer - Knowledge Graphs &amp; Semantic Technologies</t>
+          <t>SENIOR DATA ENGINEER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>US Neuro LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, SQL</t>
+          <t>Snowflake, Databricks, PostgreSQL, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,59 +1009,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d858caf7b9374cfa</t>
+          <t>https://www.indeed.com/viewjob?jk=5acff10101632d23</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DevOps Developer</t>
+          <t>Senior AI Scientist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ralph Lauren</t>
+          <t>Ochsner Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Python, SQL, R, Scala, A/B Testing</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0965aea3b361ff0b</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a95397d30aebfd</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Dev Eng I - 1Finity</t>
+          <t>Summer 2027: Finance Transformation &amp; Analytics Intern</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fujitsu</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, C++, Scala, Optimization</t>
+          <t>RAG, Redshift, BigQuery, BigQuery, Redshift, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,32 +1079,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e52f7afeb11d165</t>
+          <t>https://www.indeed.com/viewjob?jk=25d38e60ead161cc</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SAP AI Engineering Architect</t>
+          <t>Founding Developer Relations Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Python, R, Java, Scala</t>
+          <t>RAG, LLaMA, Hugging Face, PyTorch, MLflow, Kubernetes, Git, Databricks, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1114,32 +1114,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233070f0adc5585c</t>
+          <t>https://www.indeed.com/viewjob?jk=f129d025abdb71fb</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer (Java and Big Data)</t>
+          <t>Software Engineer, Full Stack, Level 5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Snap Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BigQuery, Dataflow, Kubernetes, Apache Airflow, CI/CD, Git, BigQuery, R, Java, Optimization</t>
+          <t>RAG, Kubernetes, Git, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1149,32 +1149,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9feb9788d5ad86</t>
+          <t>https://www.indeed.com/viewjob?jk=42074dc4d1142175</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer (Java/Big Data)</t>
+          <t>2027 Summer Intern – Machine Learning Engineer, AV/AI Platform</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BigQuery, Dataflow, Kubernetes, Apache Airflow, CI/CD, Git, BigQuery, R, Java, Optimization</t>
+          <t>Machine Learning Engineer, RAG, PyTorch, Kubernetes, Python, R, C++, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,32 +1184,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8a623c5a6c2d7b</t>
+          <t>https://www.indeed.com/viewjob?jk=706315aa539c48e8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Frontend Software Engineer</t>
+          <t>Software Developer in Test Intern</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TeamViewer</t>
+          <t>IDeaS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, R, Java, Scala, Optimization</t>
+          <t>Generative AI, Copilot, Git, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1219,32 +1219,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aabb4abb2994f2a1</t>
+          <t>https://www.indeed.com/viewjob?jk=a74dbef62a44c636</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>Simulation Runtime Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Git, Python, R, Java</t>
+          <t>RAG, Docker, CI/CD, Git, Python, R, Java, C++, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1254,32 +1254,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d208dd20c3dcd5</t>
+          <t>https://www.indeed.com/viewjob?jk=222eea411d768471</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Front-end Software Engineer (React)</t>
+          <t>Omniverse Platform Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Quantifind</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, Docker, Kubernetes, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, C++, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1289,32 +1289,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4feb842d36271c67</t>
+          <t>https://www.indeed.com/viewjob?jk=119911ccd31cfd1d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Rendering Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SBA Communications</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Dataflow, CI/CD, Git, Databricks, Power BI, SQL, R, Scala</t>
+          <t>RAG, Docker, CI/CD, Git, Python, R, C++, Scala, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1324,32 +1324,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ca86983beb5881</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f7f40a3d2a1ecc</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Analytics Specialist</t>
+          <t>Senior Software Engineer — Backend (Files Team)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bentley University</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, S3, Docker, Kubernetes, Databricks, R, Java, C++, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1359,42 +1359,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8592fb6d6a32c62</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>SRE Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, Git, MySQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d869fd993b2cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=34c0f4f8c0ecad6b</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-10-03.xlsx
+++ b/daily_matches/job_matches_2026-10-03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,60 +456,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Digital Software Engineer Intermediate Analyst</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>University of Phoenix</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, NoSQL</t>
+          <t>Data Scientist, RAG, LLaMA, Gemini, S3, Glue, Athena, Redshift, Data Lake, Redshift</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f502a72aa366cf5</t>
+          <t>https://www.indeed.com/viewjob?jk=231c175d9900352e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Operations Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TGS</t>
+          <t>Quarterhill</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Data Scientist, Docker, Git, Kafka, Hadoop, PostgreSQL, Tableau, Power BI, Matplotlib, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,32 +519,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6251b84b65aed773</t>
+          <t>https://www.indeed.com/viewjob?jk=80f4f1849ee69353</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Engineer, IT AI</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, LLaMA, Gemini, Copilot, Docker, Jenkins, Git, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,32 +554,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6da4b0626ba24d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=3c0579d402aad195</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Java, Angular</t>
+          <t>Full-stack Engineer 4, Cyber Identity Security</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, S3, CI/CD, Git, Kafka, MySQL, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,24 +589,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75183eedc15fcaa</t>
+          <t>https://www.indeed.com/viewjob?jk=5c73541ffb28ff13</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Advanced Software Engineer - AI Platform</t>
+          <t>Full-stack Engineer 4 (Java, Spring Boot, Python, CI/CD)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Relativity</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MLflow, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Databricks, Python, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,24 +624,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68b63ee7b7ca6842</t>
+          <t>https://www.indeed.com/viewjob?jk=cd55268246c76b99</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rice University</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, FAISS, PyTorch, S3, Data Lake, Docker, Kubernetes, Git, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,32 +659,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c35c7cc0f98c8cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=5a68879b2db22f8d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr Applied Data Scientist - Personalization (applied ML, PyTorch, RecSys)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rice Engineering</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, FAISS, PyTorch, S3, Data Lake, Docker, Kubernetes, Git, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,28 +694,28 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d79a4934cb33cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=e04bfee47b672068</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Simulation Infrastructure Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -729,32 +729,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b856865fd8381428</t>
+          <t>https://www.indeed.com/viewjob?jk=70bccfc37ad355e2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Science Co-Op (NLP &amp; GenAI)</t>
+          <t>Senior Associate, Data Scientist - Applied AI (Financial Services)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bose</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Framingham, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Hugging Face, scikit-learn, MLflow, Git, Snowflake, Databricks, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, PyTorch, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,32 +764,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19382d40f0c41f5</t>
+          <t>https://www.indeed.com/viewjob?jk=a478564c79e5c0ad</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Application/DevOps Platform Engineer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+          <t>AI Engineer, Data Scientist, RAG, Tableau, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,567 +799,42 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d78fc9cce74c619</t>
+          <t>https://www.indeed.com/viewjob?jk=d6ca13d009de67d6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, Azure ML, Snowflake, Databricks, SQL</t>
+          <t>AI Engineer, Data Scientist, RAG, Tableau, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65d759c6cb21fb15</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Sr Data Engineer - Databricks</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Georgia-Pacific</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, S3, Data Lake, CI/CD, Terraform, Git, Databricks, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3a085e8b62912626</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Developer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>HealthStream</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, EC2, CI/CD, Git, MySQL, SQL, R</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=01050adb3573b7dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Software Engineer, Backend â€“ Webex Signaling</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Git, Kafka, Cassandra, NoSQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e1b2b0f782a362c</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Caterpillar</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Peoria, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, S3, Kinesis, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Python</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c0b1ce938721b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>SENIOR DATA ENGINEER</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>US Neuro LLC</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Snowflake, Databricks, PostgreSQL, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5acff10101632d23</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior AI Scientist</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Ochsner Health</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>New Orleans, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Python, SQL, R, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a95397d30aebfd</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Summer 2027: Finance Transformation &amp; Analytics Intern</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Intuit</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Mountain View, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, BigQuery, BigQuery, Redshift, Tableau, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=25d38e60ead161cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Founding Developer Relations Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, LLaMA, Hugging Face, PyTorch, MLflow, Kubernetes, Git, Databricks, R</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f129d025abdb71fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Software Engineer, Full Stack, Level 5</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Snap Inc.</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, Git, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=42074dc4d1142175</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2027 Summer Intern – Machine Learning Engineer, AV/AI Platform</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, PyTorch, Kubernetes, Python, R, C++, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=706315aa539c48e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Software Developer in Test Intern</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>IDeaS</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Bloomington, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Generative AI, Copilot, Git, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a74dbef62a44c636</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Simulation Runtime Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Caterpillar</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, Git, Python, R, Java, C++, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=222eea411d768471</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Omniverse Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Caterpillar</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, C++, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=119911ccd31cfd1d</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Rendering Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Caterpillar</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, Git, Python, R, C++, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f7f40a3d2a1ecc</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer — Backend (Files Team)</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, S3, Docker, Kubernetes, Databricks, R, Java, C++, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=34c0f4f8c0ecad6b</t>
+          <t>https://www.indeed.com/viewjob?jk=08078bd8afaa33a1</t>
         </is>
       </c>
     </row>
